--- a/Observation_Dictionary.xlsx
+++ b/Observation_Dictionary.xlsx
@@ -9,10 +9,10 @@
   <sheets>
     <sheet name="Observations" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Templates" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Observation Language Examples" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Examples" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Observations'!$A$1:$D$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Observations'!$A$1:$C$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -77,7 +77,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -450,32 +450,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>OBS-ID</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Statement (EN)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Statement (EN)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>문장 (한글)</t>
         </is>
@@ -484,20 +478,15 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>OBS-PEL-OPEN-EARLY</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
           <t>pelvis_open_early</t>
         </is>
       </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>The Pelvis Is Open Earlier Than Normal.</t>
+        </is>
+      </c>
       <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>The Pelvis Is Open Earlier Than Normal.</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>골반이 정상보다 이른 타이밍에 열려 있다.</t>
         </is>
@@ -506,20 +495,15 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>OBS-PEL-ROT-INSUF</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
           <t>pelvis_rotation_insufficient</t>
         </is>
       </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>The Pelvis Has Rotated Less Than Normal.</t>
+        </is>
+      </c>
       <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>The Pelvis Has Rotated Less Than Normal.</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>골반이 정상보다 덜 회전해 있다.</t>
         </is>
@@ -528,20 +512,15 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>OBS-PEL-ROT-EXCESS</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
           <t>pelvis_rotation_excessive</t>
         </is>
       </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>The Pelvis Has Rotated More Than Normal.</t>
+        </is>
+      </c>
       <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>The Pelvis Has Rotated More Than Normal.</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>골반이 정상보다 더 많이 회전해 있다.</t>
         </is>
@@ -550,20 +529,15 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>OBS-PEL-STALL</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
           <t>pelvis_stall</t>
         </is>
       </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>The Pelvis Rotation Has Decelerated Earlier Than Normal.</t>
+        </is>
+      </c>
       <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>The Pelvis Rotation Has Decelerated Earlier Than Normal.</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>골반 회전이 정상보다 일찍 감속해 있다.</t>
         </is>
@@ -572,20 +546,15 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>OBS-THX-ROT-INSUF</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
           <t>thorax_rotation_insufficient</t>
         </is>
       </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>The Thorax Has Rotated Less Than Normal.</t>
+        </is>
+      </c>
       <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>The Thorax Has Rotated Less Than Normal.</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>흉곽이 정상보다 덜 회전해 있다.</t>
         </is>
@@ -594,20 +563,15 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>OBS-THX-ROT-EXCESS</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
           <t>thorax_rotation_excessive</t>
         </is>
       </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>The Thorax Has Rotated More Than Normal.</t>
+        </is>
+      </c>
       <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>The Thorax Has Rotated More Than Normal.</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>흉곽이 정상보다 더 많이 회전해 있다.</t>
         </is>
@@ -616,20 +580,15 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>OBS-THX-STALL</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
           <t>thorax_stall</t>
         </is>
       </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>The Thorax Rotation Has Decelerated Earlier Than Normal.</t>
+        </is>
+      </c>
       <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>The Thorax Rotation Has Decelerated Earlier Than Normal.</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>흉곽 회전이 정상보다 일찍 감속해 있다.</t>
         </is>
@@ -638,20 +597,15 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>OBS-THX-OPEN-EARLY</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
           <t>thorax_open_early</t>
         </is>
       </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>The Thorax Is Open Earlier Than Normal.</t>
+        </is>
+      </c>
       <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>The Thorax Is Open Earlier Than Normal.</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>흉곽이 정상보다 이른 타이밍에 열려 있다.</t>
         </is>
@@ -660,20 +614,15 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>OBS-EARLY-EXTENSION</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
           <t>early_extension</t>
         </is>
       </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>The Pelvis Has Moved Toward The Ball And The Hips Have Extended Earlier Than Normal.</t>
+        </is>
+      </c>
       <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>The Pelvis Has Moved Toward The Ball And The Hips Have Extended Earlier Than Normal.</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>골반이 볼 방향으로 이동하고 고관절이 정상보다 일찍 신전되어 있다.</t>
         </is>
@@ -682,20 +631,15 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>OBS-SPINE-EXT-EXCESS</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
           <t>spine_extension_excessive</t>
         </is>
       </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>The Spine Is More Extended Than Normal.</t>
+        </is>
+      </c>
       <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>The Spine Is More Extended Than Normal.</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>척추가 정상보다 과도하게 신전되어 있다.</t>
         </is>
@@ -704,20 +648,15 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>OBS-HEAD-ELEVATION</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
           <t>head_elevation</t>
         </is>
       </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>The Head Is Higher Than Normal.</t>
+        </is>
+      </c>
       <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>The Head Is Higher Than Normal.</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>머리가 정상보다 높은 위치에 있다.</t>
         </is>
@@ -726,20 +665,15 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>OBS-HEAD-DROP</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
           <t>head_drop</t>
         </is>
       </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>The Head Is Lower Than Normal.</t>
+        </is>
+      </c>
       <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>The Head Is Lower Than Normal.</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>머리가 정상보다 낮은 위치에 있다.</t>
         </is>
@@ -748,20 +682,15 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>OBS-HEAD-HANGING-BACK</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
           <t>head_hanging_back</t>
         </is>
       </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>The Head Is Positioned Further Toward The Trail Side Than Normal.</t>
+        </is>
+      </c>
       <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>The Head Is Positioned Further Toward The Trail Side Than Normal.</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>머리가 정상보다 트레일측(후방)에 위치해 있다.</t>
         </is>
@@ -770,20 +699,15 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>OBS-HIGH-HANDS</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
           <t>high_hands</t>
         </is>
       </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>The Hands Are Higher Than Normal Relative To Body Rotation.</t>
+        </is>
+      </c>
       <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>The Hands Are Higher Than Normal Relative To Body Rotation.</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>몸의 회전 대비 손이 정상보다 높은 위치에 있다.</t>
         </is>
@@ -792,27 +716,22 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>OBS-LOW-HANDS</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
           <t>low_hands</t>
         </is>
       </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>The Hands Are Lower Than Normal Relative To Body Rotation.</t>
+        </is>
+      </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>The Hands Are Lower Than Normal Relative To Body Rotation.</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
           <t>몸의 회전 대비 손이 정상보다 낮은 위치에 있다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D16"/>
+  <autoFilter ref="A1:C16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -940,7 +859,7 @@
   <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="48" customWidth="1" min="3" max="3"/>
   </cols>
